--- a/artifacts/reports/testcases/TC-UAT-WEB-02_VoIPWeb受入テストケース_ベトナム語版/TC-UAT-WEB-02_VoIPWeb受入テストケース_ベトナム語版.xlsx
+++ b/artifacts/reports/testcases/TC-UAT-WEB-02_VoIPWeb受入テストケース_ベトナム語版/TC-UAT-WEB-02_VoIPWeb受入テストケース_ベトナム語版.xlsx
@@ -2078,7 +2078,7 @@
       <c r="AD1" s="30" t="n"/>
       <c r="AE1" s="32" t="inlineStr">
         <is>
-          <t>種別</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="AF1" s="29" t="n"/>
@@ -2090,7 +2090,7 @@
       <c r="AL1" s="30" t="n"/>
       <c r="AM1" s="32" t="inlineStr">
         <is>
-          <t>第1回（DEV）</t>
+          <t>第1回（ローカル）</t>
         </is>
       </c>
       <c r="AN1" s="29" t="n"/>
@@ -2106,7 +2106,7 @@
       <c r="AX1" s="30" t="n"/>
       <c r="AY1" s="33" t="inlineStr">
         <is>
-          <t>第2回（PRD）</t>
+          <t>第2回（ローカル）</t>
         </is>
       </c>
       <c r="AZ1" s="29" t="n"/>
@@ -2455,7 +2455,7 @@
       <c r="AF5" s="27" t="n"/>
       <c r="AG5" s="32" t="inlineStr">
         <is>
-          <t>テスト結果 - 第1回（DEV）</t>
+          <t>テスト結果 - 第1回</t>
         </is>
       </c>
       <c r="AH5" s="29" t="n"/>
@@ -2473,7 +2473,7 @@
       <c r="AT5" s="30" t="n"/>
       <c r="AU5" s="32" t="inlineStr">
         <is>
-          <t>テスト結果 - 第2回（PRD）</t>
+          <t>テスト結果 - 第2回</t>
         </is>
       </c>
       <c r="AV5" s="29" t="n"/>
@@ -5098,7 +5098,7 @@
       <c r="BJ31" s="5" t="n"/>
       <c r="BK31" s="40" t="n"/>
     </row>
-    <row r="32" ht="60" customHeight="1">
+    <row r="32" ht="90" customHeight="1">
       <c r="A32" s="63" t="inlineStr">
         <is>
           <t>UAT-WEB-026</t>
@@ -5139,7 +5139,9 @@
       <c r="R32" s="64" t="inlineStr">
         <is>
           <t>① Chọn checkbox của tenant mục tiêu
-② Nhấn "ログイン情報通知"</t>
+② Nhấn "ログイン情報通知"
+③ Tại popup xác nhận gửi mail "メール送信の確認", nhấn nút "OK"
+④ Tại popup "ログイン情報送信確認", nhấn nút "キャンセル"</t>
         </is>
       </c>
       <c r="S32" s="5" t="n"/>
